--- a/output/graficos_regionales_correlaciones/plot_regional_correl_matriz_d_otrasrel_a_2019_arica_y_parinacota.xlsx
+++ b/output/graficos_regionales_correlaciones/plot_regional_correl_matriz_d_otrasrel_a_2019_arica_y_parinacota.xlsx
@@ -132,7 +132,7 @@
     <t xml:space="preserve">Fecha de creación</t>
   </si>
   <si>
-    <t xml:space="preserve">2026-09-18 13:56</t>
+    <t xml:space="preserve">2026-09-24 00:47</t>
   </si>
   <si>
     <t xml:space="preserve">Fuente</t>
@@ -568,7 +568,7 @@
       </c>
       <c r="E2" s="2"/>
       <c r="F2" s="2" t="n">
-        <v>-0.05</v>
+        <v>-0.04</v>
       </c>
       <c r="G2" s="2"/>
     </row>
@@ -606,7 +606,7 @@
       </c>
       <c r="E4" s="2"/>
       <c r="F4" s="2" t="n">
-        <v>-0.06</v>
+        <v>-0.05</v>
       </c>
       <c r="G4" s="2"/>
     </row>
@@ -663,7 +663,7 @@
       </c>
       <c r="E7" s="2"/>
       <c r="F7" s="2" t="n">
-        <v>0.09</v>
+        <v>0.06</v>
       </c>
       <c r="G7" s="2"/>
     </row>
@@ -682,7 +682,7 @@
       </c>
       <c r="E8" s="2"/>
       <c r="F8" s="2" t="n">
-        <v>0.18</v>
+        <v>0.15</v>
       </c>
       <c r="G8" s="2"/>
     </row>
@@ -701,7 +701,7 @@
       </c>
       <c r="E9" s="2"/>
       <c r="F9" s="2" t="n">
-        <v>0.24</v>
+        <v>0.21</v>
       </c>
       <c r="G9" s="2"/>
     </row>
@@ -758,7 +758,7 @@
       </c>
       <c r="E12" s="2"/>
       <c r="F12" s="2" t="n">
-        <v>0.05</v>
+        <v>0.07</v>
       </c>
       <c r="G12" s="2"/>
     </row>
@@ -777,7 +777,7 @@
       </c>
       <c r="E13" s="2"/>
       <c r="F13" s="2" t="n">
-        <v>0.13</v>
+        <v>0.12</v>
       </c>
       <c r="G13" s="2"/>
     </row>
@@ -796,7 +796,7 @@
       </c>
       <c r="E14" s="2"/>
       <c r="F14" s="2" t="n">
-        <v>-0.18</v>
+        <v>-0.19</v>
       </c>
       <c r="G14" s="2"/>
     </row>
@@ -815,7 +815,7 @@
       </c>
       <c r="E15" s="2"/>
       <c r="F15" s="2" t="n">
-        <v>0</v>
+        <v>0.01</v>
       </c>
       <c r="G15" s="2"/>
     </row>
@@ -834,7 +834,7 @@
       </c>
       <c r="E16" s="2"/>
       <c r="F16" s="2" t="n">
-        <v>-0.36</v>
+        <v>-0.38</v>
       </c>
       <c r="G16" s="2"/>
     </row>
@@ -891,7 +891,7 @@
       </c>
       <c r="E19" s="2"/>
       <c r="F19" s="2" t="n">
-        <v>0.08</v>
+        <v>0.12</v>
       </c>
       <c r="G19" s="2"/>
     </row>
@@ -910,7 +910,7 @@
       </c>
       <c r="E20" s="2"/>
       <c r="F20" s="2" t="n">
-        <v>0.14</v>
+        <v>0.18</v>
       </c>
       <c r="G20" s="2"/>
     </row>
@@ -1043,7 +1043,7 @@
       </c>
       <c r="E27" s="2"/>
       <c r="F27" s="2" t="n">
-        <v>0.1</v>
+        <v>0.11</v>
       </c>
       <c r="G27" s="2"/>
     </row>
@@ -1062,7 +1062,7 @@
       </c>
       <c r="E28" s="2"/>
       <c r="F28" s="2" t="n">
-        <v>-0.08</v>
+        <v>-0.07</v>
       </c>
       <c r="G28" s="2"/>
     </row>
@@ -1081,7 +1081,7 @@
       </c>
       <c r="E29" s="2"/>
       <c r="F29" s="2" t="n">
-        <v>-0.07</v>
+        <v>-0.06</v>
       </c>
       <c r="G29" s="2"/>
     </row>
@@ -1138,7 +1138,7 @@
       </c>
       <c r="E32" s="2"/>
       <c r="F32" s="2" t="n">
-        <v>0.24</v>
+        <v>0.23</v>
       </c>
       <c r="G32" s="2"/>
     </row>
@@ -1214,7 +1214,7 @@
       </c>
       <c r="E36" s="2"/>
       <c r="F36" s="2" t="n">
-        <v>-0.03</v>
+        <v>-0.02</v>
       </c>
       <c r="G36" s="2"/>
     </row>
@@ -1271,7 +1271,7 @@
       </c>
       <c r="E39" s="2"/>
       <c r="F39" s="2" t="n">
-        <v>-0.06</v>
+        <v>-0.07</v>
       </c>
       <c r="G39" s="2"/>
     </row>
@@ -1290,7 +1290,7 @@
       </c>
       <c r="E40" s="2"/>
       <c r="F40" s="2" t="n">
-        <v>0.02</v>
+        <v>0.01</v>
       </c>
       <c r="G40" s="2"/>
     </row>

--- a/output/graficos_regionales_correlaciones/plot_regional_correl_matriz_d_otrasrel_a_2019_arica_y_parinacota.xlsx
+++ b/output/graficos_regionales_correlaciones/plot_regional_correl_matriz_d_otrasrel_a_2019_arica_y_parinacota.xlsx
@@ -111,7 +111,7 @@
     <t xml:space="preserve">Migración</t>
   </si>
   <si>
-    <t xml:space="preserve">Movilidad interna (CMI)</t>
+    <t xml:space="preserve">Movilidad interna comunal (CMI)</t>
   </si>
   <si>
     <t xml:space="preserve">Saldo migratorio</t>
@@ -132,7 +132,7 @@
     <t xml:space="preserve">Fecha de creación</t>
   </si>
   <si>
-    <t xml:space="preserve">2026-09-24 00:47</t>
+    <t xml:space="preserve">2026-10-01 23:07</t>
   </si>
   <si>
     <t xml:space="preserve">Fuente</t>

--- a/output/graficos_regionales_correlaciones/plot_regional_correl_matriz_d_otrasrel_a_2019_arica_y_parinacota.xlsx
+++ b/output/graficos_regionales_correlaciones/plot_regional_correl_matriz_d_otrasrel_a_2019_arica_y_parinacota.xlsx
@@ -132,7 +132,7 @@
     <t xml:space="preserve">Fecha de creación</t>
   </si>
   <si>
-    <t xml:space="preserve">2026-10-01 23:07</t>
+    <t xml:space="preserve">2026-10-05 19:32</t>
   </si>
   <si>
     <t xml:space="preserve">Fuente</t>
